--- a/detection_mode_project/outputs/sensitivity_analysis_clean/sensitivity_analysis_tables.xlsx
+++ b/detection_mode_project/outputs/sensitivity_analysis_clean/sensitivity_analysis_tables.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icracuk-my.sharepoint.com/personal/reuben_frost_icr_ac_uk/Documents/Documents/mode_of_detection/repo/detection_mode_project/outputs/sensitivity_analysis_clean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{2A2F8162-CDF2-4864-A254-DABB595083DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{184CD7CB-DAC2-47D7-86A2-F3A64FF131E6}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{2A2F8162-CDF2-4864-A254-DABB595083DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12AA80D7-3D8D-46DB-BDAC-3AC40A10C4B2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" firstSheet="1" activeTab="3" xr2:uid="{47947C81-3C23-4AF3-97E6-5F251030FA49}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" firstSheet="2" activeTab="4" xr2:uid="{47947C81-3C23-4AF3-97E6-5F251030FA49}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
     <sheet name="Postmenopausal" sheetId="2" r:id="rId2"/>
     <sheet name="No_Time_Adjustment" sheetId="6" r:id="rId3"/>
     <sheet name="Postmenopausal_HRT_Never" sheetId="3" r:id="rId4"/>
-    <sheet name="ER_positive" sheetId="4" r:id="rId5"/>
-    <sheet name="Complete_Case" sheetId="5" r:id="rId6"/>
+    <sheet name="No_Reg_Derivation" sheetId="7" r:id="rId5"/>
+    <sheet name="ER_positive" sheetId="4" r:id="rId6"/>
+    <sheet name="Complete_Case" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4698" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5481" uniqueCount="1132">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -3459,6 +3460,494 @@
   </si>
   <si>
     <t>1.30, 3.00</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>Interval</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  
+N = 613</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>Screen-Detected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  
+N = 908</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>399</t>
+  </si>
+  <si>
+    <t>0.97, 1.74</t>
+  </si>
+  <si>
+    <t>0.81, 1.64</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>0.66, 1.30</t>
+  </si>
+  <si>
+    <t>0.58, 1.31</t>
+  </si>
+  <si>
+    <t>Oral contraceptive use</t>
+  </si>
+  <si>
+    <t>Ever</t>
+  </si>
+  <si>
+    <t>532</t>
+  </si>
+  <si>
+    <t>757</t>
+  </si>
+  <si>
+    <t>0.83, 1.61</t>
+  </si>
+  <si>
+    <t>1.31</t>
+  </si>
+  <si>
+    <t>0.89, 1.96</t>
+  </si>
+  <si>
+    <t>Parity</t>
+  </si>
+  <si>
+    <t>1.53</t>
+  </si>
+  <si>
+    <t>0.73, 3.21</t>
+  </si>
+  <si>
+    <t>0.57, 3.48</t>
+  </si>
+  <si>
+    <t>484</t>
+  </si>
+  <si>
+    <t>0.66, 2.51</t>
+  </si>
+  <si>
+    <t>0.60, 3.13</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>0.59, 2.31</t>
+  </si>
+  <si>
+    <t>0.57, 3.15</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>0.47, 1.49</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
+    <t>0.44, 1.40</t>
+  </si>
+  <si>
+    <t>0.39, 1.64</t>
+  </si>
+  <si>
+    <t>0.45, 1.58</t>
+  </si>
+  <si>
+    <t>0.45, 2.13</t>
+  </si>
+  <si>
+    <t>0.34, 1.55</t>
+  </si>
+  <si>
+    <t>0.32, 2.00</t>
+  </si>
+  <si>
+    <t>Breast feeding duration (mths)</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>0.86, 1.75</t>
+  </si>
+  <si>
+    <t>0.82, 1.95</t>
+  </si>
+  <si>
+    <t>6-12</t>
+  </si>
+  <si>
+    <t>0.79, 1.73</t>
+  </si>
+  <si>
+    <t>0.69, 1.82</t>
+  </si>
+  <si>
+    <t>12-24</t>
+  </si>
+  <si>
+    <t>0.58, 1.57</t>
+  </si>
+  <si>
+    <t>24+</t>
+  </si>
+  <si>
+    <t>1.08, 3.05</t>
+  </si>
+  <si>
+    <t>0.96, 3.52</t>
+  </si>
+  <si>
+    <t>Menopausal status</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
+    <t>679</t>
+  </si>
+  <si>
+    <t>0.47, 1.14</t>
+  </si>
+  <si>
+    <t>0.44, 1.34</t>
+  </si>
+  <si>
+    <t>458</t>
+  </si>
+  <si>
+    <t>0.71, 1.34</t>
+  </si>
+  <si>
+    <t>0.67, 1.42</t>
+  </si>
+  <si>
+    <t>1.65</t>
+  </si>
+  <si>
+    <t>1.01, 2.69</t>
+  </si>
+  <si>
+    <t>1.76</t>
+  </si>
+  <si>
+    <t>1.01, 3.07</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>0.66, 1.25</t>
+  </si>
+  <si>
+    <t>0.63, 1.33</t>
+  </si>
+  <si>
+    <t>1.05, 2.03</t>
+  </si>
+  <si>
+    <t>0.99, 2.16</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>637</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>1.20, 1.90</t>
+  </si>
+  <si>
+    <t>0.92, 1.63</t>
+  </si>
+  <si>
+    <t>Family history of breast cancer</t>
+  </si>
+  <si>
+    <t>714</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>0.96, 1.61</t>
+  </si>
+  <si>
+    <t>0.83, 1.57</t>
+  </si>
+  <si>
+    <t>0.004</t>
+  </si>
+  <si>
+    <t>1.87</t>
+  </si>
+  <si>
+    <t>0.43, 9.61</t>
+  </si>
+  <si>
+    <t>2.51</t>
+  </si>
+  <si>
+    <t>0.48, 14.3</t>
+  </si>
+  <si>
+    <t>348</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>0.50, 0.84</t>
+  </si>
+  <si>
+    <t>0.52, 0.98</t>
+  </si>
+  <si>
+    <t>0.45, 0.87</t>
+  </si>
+  <si>
+    <t>0.50, 1.18</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>BMI at age 20</t>
+  </si>
+  <si>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>1.07, 2.52</t>
+  </si>
+  <si>
+    <t>1.82</t>
+  </si>
+  <si>
+    <t>1.10, 3.01</t>
+  </si>
+  <si>
+    <t>629</t>
+  </si>
+  <si>
+    <t>0.47, 1.43</t>
+  </si>
+  <si>
+    <t>0.58, 2.17</t>
+  </si>
+  <si>
+    <t>2.33</t>
+  </si>
+  <si>
+    <t>0.82, 6.77</t>
+  </si>
+  <si>
+    <t>2.73</t>
+  </si>
+  <si>
+    <t>0.78, 9.08</t>
+  </si>
+  <si>
+    <t>Physical activity (MET h/wk)</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>0.69, 1.38</t>
+  </si>
+  <si>
+    <t>0.54, 1.28</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>0.73, 1.44</t>
+  </si>
+  <si>
+    <t>Alcohol units per week</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>0.70, 1.33</t>
+  </si>
+  <si>
+    <t>0.68, 1.49</t>
+  </si>
+  <si>
+    <t>0.78, 1.48</t>
+  </si>
+  <si>
+    <t>0.70, 1.57</t>
+  </si>
+  <si>
+    <t>0.63, 1.32</t>
+  </si>
+  <si>
+    <t>0.56, 1.39</t>
+  </si>
+  <si>
+    <t>0.60, 1.37</t>
+  </si>
+  <si>
+    <t>0.47, 1.35</t>
+  </si>
+  <si>
+    <t>541</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>0.83, 1.35</t>
+  </si>
+  <si>
+    <t>1.03, 1.87</t>
+  </si>
+  <si>
+    <t>0.46, 1.23</t>
+  </si>
+  <si>
+    <t>0.39, 1.44</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>0.92, 2.08</t>
+  </si>
+  <si>
+    <t>1.16, 2.62</t>
+  </si>
+  <si>
+    <t>2.18</t>
+  </si>
+  <si>
+    <t>1.40, 3.42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Model 1: Age at menarche, Menopause, Age at menopause, MHT status, Oral contraceptive use, Parity, Age at first birth, Breast feeding duration (mths), Benign breast disease, Family history of breast cancer, BMI at entry, BMI at age 20, Physical activity (MET h/wk), Alcohol units per week, Smoking status, Age at Diagnosis, Time from Recruitment to BC diagnosis, Year of diagnosis</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Model 2: Age at menarche, Menopause, Age at menopause, MHT status, Oral contraceptive use, Parity, Age at first birth, Breast feeding duration (mths), Benign breast disease, Family history of breast cancer, BMI at entry, BMI at age 20, Physical activity (MET h/wk), Alcohol units per week, Smoking status, Age at Diagnosis, Time from Recruitment to BC diagnosis, Year of diagnosis Percent Mammographic density (quartiles), Time from Mammographic density measurement to BRCA diagnosis.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8984,7 +9473,7 @@
   <dimension ref="A1:I87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -14070,12 +14559,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874ABD52-1AF7-416C-AD7E-B5699210F3EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E12FF98-1980-4ED7-A5E3-B50C419684FD}">
   <dimension ref="A1:I87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.90625" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -14112,10 +14600,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>645</v>
+        <v>998</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>646</v>
+        <v>999</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>8</v>
@@ -14153,7 +14641,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>14</v>
+        <v>232</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>2</v>
@@ -14162,7 +14650,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>468</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -14170,10 +14658,10 @@
         <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>615</v>
+        <v>285</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>647</v>
+        <v>224</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
@@ -14199,25 +14687,25 @@
         <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>648</v>
+        <v>416</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>649</v>
+        <v>1000</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>281</v>
+        <v>917</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>282</v>
+        <v>1001</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>650</v>
+        <v>1002</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>2</v>
@@ -14228,25 +14716,25 @@
         <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>251</v>
+        <v>1003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>186</v>
+        <v>1004</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>651</v>
+        <v>1005</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>652</v>
+        <v>1006</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>2</v>
@@ -14257,10 +14745,10 @@
         <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>100</v>
+        <v>583</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>523</v>
+        <v>343</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>2</v>
@@ -14283,7 +14771,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>36</v>
+        <v>1007</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>2</v>
@@ -14298,7 +14786,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>51</v>
+        <v>468</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>2</v>
@@ -14307,18 +14795,18 @@
         <v>2</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>171</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>234</v>
+        <v>515</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>653</v>
+        <v>271</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
@@ -14341,28 +14829,28 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>41</v>
+        <v>1008</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>654</v>
+        <v>1009</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>655</v>
+        <v>1010</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>656</v>
+        <v>1011</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>370</v>
+        <v>1012</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>657</v>
+        <v>1013</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>2</v>
@@ -14373,10 +14861,10 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>2</v>
@@ -14399,7 +14887,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>50</v>
+        <v>1014</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>2</v>
@@ -14414,7 +14902,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>75</v>
+        <v>468</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>2</v>
@@ -14431,10 +14919,10 @@
         <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>134</v>
+        <v>536</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>658</v>
+        <v>94</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
@@ -14460,25 +14948,25 @@
         <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>659</v>
+        <v>101</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>620</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>368</v>
+        <v>1015</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>660</v>
+        <v>1016</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>480</v>
+        <v>311</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>661</v>
+        <v>1017</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>2</v>
@@ -14489,25 +14977,25 @@
         <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>436</v>
+        <v>156</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>662</v>
+        <v>1018</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>411</v>
+        <v>60</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>663</v>
+        <v>1019</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>664</v>
+        <v>1020</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>2</v>
@@ -14518,25 +15006,25 @@
         <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>501</v>
+        <v>1021</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>665</v>
+        <v>1022</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>368</v>
+        <v>477</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>666</v>
+        <v>1023</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>195</v>
+        <v>871</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>667</v>
+        <v>1024</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>2</v>
@@ -14559,7 +15047,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>270</v>
+        <v>52</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>2</v>
@@ -14568,7 +15056,7 @@
         <v>2</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -14576,10 +15064,10 @@
         <v>76</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>379</v>
+        <v>1025</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>340</v>
+        <v>77</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
@@ -14605,25 +15093,25 @@
         <v>79</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>668</v>
+        <v>55</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>669</v>
+        <v>186</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>670</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>671</v>
+        <v>1026</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>303</v>
+        <v>970</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>672</v>
+        <v>85</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>2</v>
@@ -14634,25 +15122,25 @@
         <v>86</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>673</v>
+        <v>1027</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>674</v>
+        <v>1028</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>158</v>
+        <v>670</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>675</v>
+        <v>1029</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>130</v>
+        <v>542</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>676</v>
+        <v>1030</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>2</v>
@@ -14663,25 +15151,25 @@
         <v>93</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>39</v>
+        <v>507</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>459</v>
+        <v>501</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>480</v>
+        <v>291</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>677</v>
+        <v>1031</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>508</v>
+        <v>130</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>678</v>
+        <v>1032</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>2</v>
@@ -14692,25 +15180,25 @@
         <v>99</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>340</v>
+        <v>520</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>640</v>
+        <v>444</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>679</v>
+        <v>1033</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>510</v>
+        <v>102</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>680</v>
+        <v>1034</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>2</v>
@@ -14721,10 +15209,10 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>681</v>
+        <v>384</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>440</v>
+        <v>318</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>2</v>
@@ -14747,7 +15235,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
-        <v>108</v>
+        <v>1035</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>2</v>
@@ -14762,7 +15250,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>2</v>
@@ -14779,10 +15267,10 @@
         <v>110</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>682</v>
+        <v>394</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>683</v>
+        <v>435</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
@@ -14805,28 +15293,28 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>113</v>
+        <v>1036</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>684</v>
+        <v>779</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>685</v>
+        <v>1037</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>420</v>
+        <v>64</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>686</v>
+        <v>1038</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>687</v>
+        <v>203</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>688</v>
+        <v>1039</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>2</v>
@@ -14834,28 +15322,28 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
-        <v>119</v>
+        <v>1040</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>350</v>
+        <v>632</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>689</v>
+        <v>16</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>392</v>
+        <v>477</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>690</v>
+        <v>1041</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>510</v>
+        <v>122</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>691</v>
+        <v>1042</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>2</v>
@@ -14863,13 +15351,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>126</v>
+        <v>1043</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>313</v>
+        <v>460</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>692</v>
+        <v>814</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>370</v>
@@ -14881,10 +15369,10 @@
         <v>2</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>243</v>
+        <v>480</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>694</v>
+        <v>1044</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>2</v>
@@ -14892,28 +15380,28 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>132</v>
+        <v>1045</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>695</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>234</v>
+        <v>890</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>193</v>
+        <v>237</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>696</v>
+        <v>1046</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>697</v>
+        <v>164</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>698</v>
+        <v>1047</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>2</v>
@@ -14924,10 +15412,10 @@
         <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>134</v>
+        <v>536</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>658</v>
+        <v>94</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>2</v>
@@ -14950,7 +15438,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
-        <v>139</v>
+        <v>1048</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>2</v>
@@ -14974,7 +15462,7 @@
         <v>2</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -14982,10 +15470,10 @@
         <v>141</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>699</v>
+        <v>814</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>700</v>
+        <v>1049</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
@@ -15011,25 +15499,25 @@
         <v>144</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>701</v>
+        <v>1050</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>702</v>
+        <v>1051</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>84</v>
+        <v>970</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>703</v>
+        <v>1052</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>704</v>
+        <v>1053</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>2</v>
@@ -15052,7 +15540,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>705</v>
+        <v>109</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>2</v>
@@ -15061,7 +15549,7 @@
         <v>2</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>706</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -15069,10 +15557,10 @@
         <v>153</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>484</v>
+        <v>39</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>707</v>
+        <v>181</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
@@ -15098,25 +15586,25 @@
         <v>155</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>708</v>
+        <v>648</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>709</v>
+        <v>1054</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>243</v>
+        <v>178</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>710</v>
+        <v>1055</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>711</v>
+        <v>1056</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>2</v>
@@ -15127,25 +15615,25 @@
         <v>161</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>583</v>
+        <v>890</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>34</v>
+        <v>242</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>712</v>
+        <v>1057</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>713</v>
+        <v>1058</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>237</v>
+        <v>1059</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>714</v>
+        <v>1060</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>2</v>
@@ -15156,10 +15644,10 @@
         <v>33</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>616</v>
+        <v>869</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>715</v>
+        <v>665</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>2</v>
@@ -15197,7 +15685,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>705</v>
+        <v>1061</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>2</v>
@@ -15206,7 +15694,7 @@
         <v>2</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>716</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -15214,10 +15702,10 @@
         <v>171</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>435</v>
+        <v>920</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>115</v>
+        <v>582</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>18</v>
@@ -15243,25 +15731,25 @@
         <v>174</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>35</v>
+        <v>790</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>717</v>
+        <v>1063</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>391</v>
+        <v>1064</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>2</v>
@@ -15272,25 +15760,25 @@
         <v>180</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>718</v>
+        <v>390</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>424</v>
+        <v>653</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>719</v>
+        <v>193</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>720</v>
+        <v>1065</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>721</v>
+        <v>193</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>722</v>
+        <v>1066</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>2</v>
@@ -15301,10 +15789,10 @@
         <v>33</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>154</v>
+        <v>40</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>715</v>
+        <v>567</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>2</v>
@@ -15351,18 +15839,18 @@
         <v>2</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>14</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>171</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>723</v>
+        <v>1067</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>702</v>
+        <v>1068</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>18</v>
@@ -15385,28 +15873,28 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>1008</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>114</v>
+        <v>1069</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>700</v>
+        <v>255</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>578</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>724</v>
+        <v>1070</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>725</v>
+        <v>1071</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>2</v>
@@ -15414,7 +15902,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
-        <v>197</v>
+        <v>1072</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>2</v>
@@ -15429,7 +15917,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>726</v>
+        <v>13</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>2</v>
@@ -15438,7 +15926,7 @@
         <v>2</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
@@ -15446,10 +15934,10 @@
         <v>38</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>727</v>
+        <v>1054</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>728</v>
+        <v>1073</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>18</v>
@@ -15475,25 +15963,25 @@
         <v>41</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>658</v>
+        <v>459</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>633</v>
+        <v>1074</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>46</v>
+        <v>420</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>729</v>
+        <v>1075</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>281</v>
+        <v>508</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>730</v>
+        <v>1076</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>2</v>
@@ -15516,7 +16004,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>731</v>
+        <v>1077</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>2</v>
@@ -15525,7 +16013,7 @@
         <v>2</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>37</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -15533,25 +16021,25 @@
         <v>208</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>267</v>
+        <v>443</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>49</v>
+        <v>210</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>732</v>
+        <v>1078</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>733</v>
+        <v>1079</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>734</v>
+        <v>1080</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>735</v>
+        <v>1081</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>2</v>
@@ -15562,10 +16050,10 @@
         <v>215</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>736</v>
+        <v>1082</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>737</v>
+        <v>1083</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
@@ -15591,25 +16079,25 @@
         <v>217</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>674</v>
+        <v>700</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>568</v>
+        <v>532</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>738</v>
+        <v>1084</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>361</v>
+        <v>303</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>739</v>
+        <v>1085</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>2</v>
@@ -15620,25 +16108,25 @@
         <v>223</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>531</v>
+        <v>484</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>360</v>
+        <v>95</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>291</v>
+        <v>595</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>740</v>
+        <v>1086</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>480</v>
+        <v>225</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>741</v>
+        <v>1087</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>2</v>
@@ -15649,10 +16137,10 @@
         <v>33</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>317</v>
+        <v>229</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>742</v>
+        <v>1088</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>2</v>
@@ -15675,7 +16163,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
-        <v>231</v>
+        <v>1089</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>2</v>
@@ -15690,7 +16178,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>743</v>
+        <v>1090</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>2</v>
@@ -15699,7 +16187,7 @@
         <v>2</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>14</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
@@ -15707,25 +16195,25 @@
         <v>208</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>744</v>
+        <v>659</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>34</v>
+        <v>583</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>745</v>
+        <v>1092</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>455</v>
+        <v>1093</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>746</v>
+        <v>1094</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>2</v>
@@ -15736,10 +16224,10 @@
         <v>215</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>747</v>
+        <v>879</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>748</v>
+        <v>1095</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>18</v>
@@ -15765,25 +16253,25 @@
         <v>217</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>337</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>749</v>
+        <v>1096</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>584</v>
+        <v>71</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>750</v>
+        <v>1097</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>2</v>
@@ -15794,25 +16282,25 @@
         <v>223</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>751</v>
+        <v>1098</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>752</v>
+        <v>1099</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>753</v>
+        <v>1100</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>754</v>
+        <v>1101</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>2</v>
@@ -15823,10 +16311,10 @@
         <v>33</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>382</v>
+        <v>615</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>2</v>
@@ -15849,7 +16337,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
-        <v>253</v>
+        <v>1102</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>2</v>
@@ -15864,7 +16352,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>2</v>
@@ -15873,7 +16361,7 @@
         <v>2</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>52</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
@@ -15881,10 +16369,10 @@
         <v>254</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>359</v>
+        <v>120</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>472</v>
+        <v>1103</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>18</v>
@@ -15910,25 +16398,25 @@
         <v>256</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>469</v>
+        <v>1104</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>692</v>
+        <v>112</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>337</v>
+        <v>178</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>755</v>
+        <v>1105</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>373</v>
+        <v>291</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>756</v>
+        <v>1106</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>2</v>
@@ -15939,16 +16427,16 @@
         <v>261</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>757</v>
+        <v>1107</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>508</v>
+        <v>275</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>758</v>
+        <v>276</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>2</v>
@@ -15957,7 +16445,7 @@
         <v>265</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>759</v>
+        <v>1108</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>2</v>
@@ -15968,10 +16456,10 @@
         <v>33</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>443</v>
+        <v>317</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>209</v>
+        <v>267</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>2</v>
@@ -15994,7 +16482,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
-        <v>268</v>
+        <v>1109</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>2</v>
@@ -16009,7 +16497,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>2</v>
@@ -16018,7 +16506,7 @@
         <v>2</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
@@ -16026,10 +16514,10 @@
         <v>53</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>615</v>
+        <v>790</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>633</v>
+        <v>1110</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>18</v>
@@ -16058,22 +16546,22 @@
         <v>366</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>28</v>
+        <v>166</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>275</v>
+        <v>130</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>760</v>
+        <v>1111</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>281</v>
+        <v>176</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>761</v>
+        <v>1112</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>2</v>
@@ -16084,25 +16572,25 @@
         <v>278</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>395</v>
+        <v>69</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>762</v>
+        <v>114</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>203</v>
+        <v>573</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>763</v>
+        <v>1113</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>687</v>
+        <v>298</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>764</v>
+        <v>1114</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>2</v>
@@ -16113,25 +16601,25 @@
         <v>284</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>765</v>
+        <v>507</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>95</v>
+        <v>385</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>337</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>766</v>
+        <v>1115</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>158</v>
+        <v>373</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>767</v>
+        <v>1116</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>2</v>
@@ -16142,25 +16630,25 @@
         <v>223</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>768</v>
+        <v>640</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>35</v>
+        <v>350</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>337</v>
+        <v>243</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>769</v>
+        <v>1117</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>370</v>
+        <v>102</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>770</v>
+        <v>1118</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>2</v>
@@ -16183,7 +16671,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>2</v>
@@ -16192,7 +16680,7 @@
         <v>2</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>109</v>
+        <v>706</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
@@ -16200,10 +16688,10 @@
         <v>171</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>771</v>
+        <v>20</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>772</v>
+        <v>1119</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>18</v>
@@ -16229,25 +16717,25 @@
         <v>174</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>461</v>
+        <v>1120</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>773</v>
+        <v>821</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>265</v>
+        <v>124</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>774</v>
+        <v>1121</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>584</v>
+        <v>517</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>775</v>
+        <v>1122</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>2</v>
@@ -16261,22 +16749,22 @@
         <v>571</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>384</v>
+        <v>695</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>225</v>
+        <v>89</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>776</v>
+        <v>1123</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>568</v>
+        <v>89</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>777</v>
+        <v>1124</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>2</v>
@@ -16337,7 +16825,7 @@
         <v>2</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>189</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
@@ -16345,10 +16833,10 @@
         <v>48</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>619</v>
+        <v>133</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>673</v>
+        <v>252</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>2</v>
@@ -16374,10 +16862,10 @@
         <v>49</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>234</v>
+        <v>592</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>2</v>
@@ -16389,10 +16877,10 @@
         <v>2</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>499</v>
+        <v>66</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>778</v>
+        <v>1126</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>2</v>
@@ -16403,10 +16891,10 @@
         <v>210</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>681</v>
+        <v>382</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>779</v>
+        <v>869</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>2</v>
@@ -16418,10 +16906,10 @@
         <v>2</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>780</v>
+        <v>712</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>781</v>
+        <v>1127</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>2</v>
@@ -16432,10 +16920,10 @@
         <v>317</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>523</v>
+        <v>718</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>2</v>
@@ -16447,10 +16935,10 @@
         <v>2</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>782</v>
+        <v>1128</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>783</v>
+        <v>1129</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>2</v>
@@ -16461,10 +16949,10 @@
         <v>33</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>784</v>
+        <v>830</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>785</v>
+        <v>181</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>2</v>
@@ -16516,7 +17004,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
-        <v>324</v>
+        <v>1130</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>2</v>
@@ -16574,7 +17062,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
-        <v>326</v>
+        <v>1131</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>2</v>
@@ -16616,6 +17104,2552 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874ABD52-1AF7-416C-AD7E-B5699210F3EC}">
+  <dimension ref="A1:I87"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="46" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H84" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I84" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I86" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A87:I87"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="A85:I85"/>
+    <mergeCell ref="A86:I86"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B548A0AB-9595-4FAA-9F2E-E5D0C85EC9E7}">
   <dimension ref="A1:I87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
